--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.39709255550232</v>
+        <v>1.689527540269127</v>
       </c>
       <c r="D2" t="n">
-        <v>5.830951894845301</v>
+        <v>0.9475296829123614</v>
       </c>
       <c r="E2" t="n">
-        <v>15.58899285466727</v>
+        <v>2.533211338883431</v>
       </c>
       <c r="F2" t="n">
-        <v>16.74098037415696</v>
+        <v>2.720409310800506</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.74998884355844</v>
+        <v>4.021873187078246</v>
       </c>
       <c r="D3" t="n">
-        <v>24.98982486839875</v>
+        <v>4.060846541114797</v>
       </c>
       <c r="E3" t="n">
-        <v>15.58899285466727</v>
+        <v>2.533211338883431</v>
       </c>
       <c r="F3" t="n">
-        <v>16.74098037415696</v>
+        <v>2.720409310800506</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.00833101980363</v>
+        <v>2.43885379071809</v>
       </c>
       <c r="D4" t="n">
-        <v>15.9696417605075</v>
+        <v>2.595066786082469</v>
       </c>
       <c r="E4" t="n">
-        <v>15.58899285466727</v>
+        <v>2.533211338883431</v>
       </c>
       <c r="F4" t="n">
-        <v>16.74098037415696</v>
+        <v>2.720409310800506</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.766928891578866</v>
+        <v>1.099625944881566</v>
       </c>
       <c r="D5" t="n">
-        <v>5.851922925187721</v>
+        <v>0.9509374753430048</v>
       </c>
       <c r="E5" t="n">
-        <v>15.58899285466727</v>
+        <v>2.533211338883431</v>
       </c>
       <c r="F5" t="n">
-        <v>16.74098037415696</v>
+        <v>2.720409310800506</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.22888225483509</v>
+        <v>6.862193366410703</v>
       </c>
       <c r="D6" t="n">
-        <v>41.96048991472012</v>
+        <v>6.81857961114202</v>
       </c>
       <c r="E6" t="n">
-        <v>15.58899285466727</v>
+        <v>2.533211338883431</v>
       </c>
       <c r="F6" t="n">
-        <v>16.74098037415696</v>
+        <v>2.720409310800506</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.73053735737505</v>
+        <v>4.831212320573445</v>
       </c>
       <c r="D7" t="n">
-        <v>29.28609876131501</v>
+        <v>4.758991048713689</v>
       </c>
       <c r="E7" t="n">
-        <v>15.58899285466727</v>
+        <v>2.533211338883431</v>
       </c>
       <c r="F7" t="n">
-        <v>16.74098037415696</v>
+        <v>2.720409310800506</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.67261752992875</v>
+        <v>1.896800348613422</v>
       </c>
       <c r="D8" t="n">
-        <v>7.022215408330651</v>
+        <v>1.141110003853731</v>
       </c>
       <c r="E8" t="n">
-        <v>15.58899285466727</v>
+        <v>2.533211338883431</v>
       </c>
       <c r="F8" t="n">
-        <v>16.74098037415696</v>
+        <v>2.720409310800506</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.88854381999832</v>
+        <v>2.906888370749727</v>
       </c>
       <c r="D9" t="n">
-        <v>14.12496020150102</v>
+        <v>2.295306032743917</v>
       </c>
       <c r="E9" t="n">
-        <v>15.58899285466727</v>
+        <v>2.533211338883431</v>
       </c>
       <c r="F9" t="n">
-        <v>16.74098037415696</v>
+        <v>2.720409310800506</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>63.23373084073095</v>
+        <v>10.27548126161878</v>
       </c>
       <c r="D10" t="n">
-        <v>63.39014286672977</v>
+        <v>10.30089821584359</v>
       </c>
       <c r="E10" t="n">
-        <v>15.58899285466727</v>
+        <v>2.533211338883431</v>
       </c>
       <c r="F10" t="n">
-        <v>16.74098037415696</v>
+        <v>2.720409310800506</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.10851870596487</v>
+        <v>5.705134289719291</v>
       </c>
       <c r="D11" t="n">
-        <v>35.48169623069555</v>
+        <v>5.765775637488026</v>
       </c>
       <c r="E11" t="n">
-        <v>15.58899285466727</v>
+        <v>2.533211338883431</v>
       </c>
       <c r="F11" t="n">
-        <v>16.74098037415696</v>
+        <v>2.720409310800506</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.63690086301846</v>
+        <v>6.7659963902405</v>
       </c>
       <c r="D12" t="n">
-        <v>41.61828295358646</v>
+        <v>6.762970979957799</v>
       </c>
       <c r="E12" t="n">
-        <v>15.58899285466727</v>
+        <v>2.533211338883431</v>
       </c>
       <c r="F12" t="n">
-        <v>16.74098037415696</v>
+        <v>2.720409310800506</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>37.58615500485178</v>
+        <v>6.107750188288414</v>
       </c>
       <c r="D13" t="n">
-        <v>37.7161694451252</v>
+        <v>6.128877534832845</v>
       </c>
       <c r="E13" t="n">
-        <v>15.58899285466727</v>
+        <v>2.533211338883431</v>
       </c>
       <c r="F13" t="n">
-        <v>16.74098037415696</v>
+        <v>2.720409310800506</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>37.01926866844423</v>
+        <v>6.015631158622188</v>
       </c>
       <c r="D14" t="n">
-        <v>37.53706384088819</v>
+        <v>6.099772874144331</v>
       </c>
       <c r="E14" t="n">
-        <v>15.58899285466727</v>
+        <v>2.533211338883431</v>
       </c>
       <c r="F14" t="n">
-        <v>16.74098037415696</v>
+        <v>2.720409310800506</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
